--- a/tests/fixtures/output/经营分析报告_2026-04-13.xlsx
+++ b/tests/fixtures/output/经营分析报告_2026-04-13.xlsx
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>分析日期：2026-04-14</t>
+          <t>分析日期：2026-04-15</t>
         </is>
       </c>
     </row>
